--- a/TABLEAU DE SYNTHESE Ewan PERSUANNE DECAMP.xlsx
+++ b/TABLEAU DE SYNTHESE Ewan PERSUANNE DECAMP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\BTS\Portfolio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\BTS\Portfolio\PortFolio Ewan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5997D2DF-BB43-490B-BA19-0765E3C5041A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{829D3C62-F58F-457F-AD4D-8435519C1510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="420" yWindow="3030" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
@@ -107,9 +107,6 @@
     <t>Réalisations en milieu professionnel en cours de seconde année</t>
   </si>
   <si>
-    <t>Adresse URL du portfolio :</t>
-  </si>
-  <si>
     <t>X</t>
   </si>
   <si>
@@ -135,6 +132,9 @@
   </si>
   <si>
     <t>SESSION 2027</t>
+  </si>
+  <si>
+    <t>Adresse URL du portfolio : https://ewan6062.github.io/PortFolio/</t>
   </si>
 </sst>
 </file>
@@ -606,7 +606,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -677,9 +677,6 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -745,6 +742,10 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1065,83 +1066,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="H1" s="25"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="32" t="s">
+      <c r="A3" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="27"/>
-      <c r="H3" s="33"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="32"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="31"/>
+      <c r="A4" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="30"/>
       <c r="F4" s="14" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="46"/>
+      <c r="A5" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="45"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="41" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1164,8 +1165,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="35"/>
-      <c r="B7" s="43"/>
+      <c r="A7" s="34"/>
+      <c r="B7" s="42"/>
       <c r="C7" s="8" t="s">
         <v>9</v>
       </c>
@@ -1221,16 +1222,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="38"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="37"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1267,60 +1268,60 @@
       <c r="AP8"/>
       <c r="AQ8"/>
     </row>
-    <row r="9" spans="1:43" s="2" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="24" t="s">
-        <v>28</v>
+    <row r="9" spans="1:43" s="47" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
       <c r="F9" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G9" s="17"/>
       <c r="H9" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9"/>
-      <c r="J9"/>
-      <c r="K9"/>
-      <c r="L9"/>
-      <c r="M9"/>
-      <c r="N9"/>
-      <c r="O9"/>
-      <c r="P9"/>
-      <c r="Q9"/>
-      <c r="R9"/>
-      <c r="S9"/>
-      <c r="T9"/>
-      <c r="U9"/>
-      <c r="V9"/>
-      <c r="W9"/>
-      <c r="X9"/>
-      <c r="Y9"/>
-      <c r="Z9"/>
-      <c r="AA9"/>
-      <c r="AB9"/>
-      <c r="AC9"/>
-      <c r="AD9"/>
-      <c r="AE9"/>
-      <c r="AF9"/>
-      <c r="AG9"/>
-      <c r="AH9"/>
-      <c r="AI9"/>
-      <c r="AJ9"/>
-      <c r="AK9"/>
-      <c r="AL9"/>
-      <c r="AM9"/>
-      <c r="AN9"/>
-      <c r="AO9"/>
-      <c r="AP9"/>
-      <c r="AQ9"/>
+        <v>21</v>
+      </c>
+      <c r="I9" s="46"/>
+      <c r="J9" s="46"/>
+      <c r="K9" s="46"/>
+      <c r="L9" s="46"/>
+      <c r="M9" s="46"/>
+      <c r="N9" s="46"/>
+      <c r="O9" s="46"/>
+      <c r="P9" s="46"/>
+      <c r="Q9" s="46"/>
+      <c r="R9" s="46"/>
+      <c r="S9" s="46"/>
+      <c r="T9" s="46"/>
+      <c r="U9" s="46"/>
+      <c r="V9" s="46"/>
+      <c r="W9" s="46"/>
+      <c r="X9" s="46"/>
+      <c r="Y9" s="46"/>
+      <c r="Z9" s="46"/>
+      <c r="AA9" s="46"/>
+      <c r="AB9" s="46"/>
+      <c r="AC9" s="46"/>
+      <c r="AD9" s="46"/>
+      <c r="AE9" s="46"/>
+      <c r="AF9" s="46"/>
+      <c r="AG9" s="46"/>
+      <c r="AH9" s="46"/>
+      <c r="AI9" s="46"/>
+      <c r="AJ9" s="46"/>
+      <c r="AK9" s="46"/>
+      <c r="AL9" s="46"/>
+      <c r="AM9" s="46"/>
+      <c r="AN9" s="46"/>
+      <c r="AO9" s="46"/>
+      <c r="AP9" s="46"/>
+      <c r="AQ9" s="46"/>
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="11"/>
@@ -1728,16 +1729,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A19" s="39" t="s">
+      <c r="A19" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="40"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="41"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="40"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -2090,16 +2091,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A27" s="39" t="s">
+      <c r="A27" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="40"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="41"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="40"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2560,7 +2561,7 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="48" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="49" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>